--- a/Database/Automation_856_Workflow_Data.xlsx
+++ b/Database/Automation_856_Workflow_Data.xlsx
@@ -1,41 +1,207 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Logs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User_Credentials" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email_Templates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference_Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Order_Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Error_Logs" sheetId="2" r:id="rId4"/>
+    <sheet name="User_Credentials" sheetId="3" r:id="rId5"/>
+    <sheet name="Email_Templates" sheetId="4" r:id="rId6"/>
+    <sheet name="Reference_Data" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+  <si>
+    <t>OrderID</t>
+  </si>
+  <si>
+    <t>StatusCode</t>
+  </si>
+  <si>
+    <t>DistributionCenter</t>
+  </si>
+  <si>
+    <t>OrderDate</t>
+  </si>
+  <si>
+    <t>ORD001</t>
+  </si>
+  <si>
+    <t>DC01</t>
+  </si>
+  <si>
+    <t>2024-01-10</t>
+  </si>
+  <si>
+    <t>ORD002</t>
+  </si>
+  <si>
+    <t>DC02</t>
+  </si>
+  <si>
+    <t>2024-01-11</t>
+  </si>
+  <si>
+    <t>ORD003</t>
+  </si>
+  <si>
+    <t>DC03</t>
+  </si>
+  <si>
+    <t>2024-01-12</t>
+  </si>
+  <si>
+    <t>ErrorID</t>
+  </si>
+  <si>
+    <t>ErrorDescription</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>ERR001</t>
+  </si>
+  <si>
+    <t>Failed to update status</t>
+  </si>
+  <si>
+    <t>2024-01-11 10:30</t>
+  </si>
+  <si>
+    <t>ERR002</t>
+  </si>
+  <si>
+    <t>Incomplete transaction</t>
+  </si>
+  <si>
+    <t>2024-01-12 14:15</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>AccessLevel</t>
+  </si>
+  <si>
+    <t>user_dc01</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>user_dc02</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Restricted</t>
+  </si>
+  <si>
+    <t>TemplateID</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>TMP001</t>
+  </si>
+  <si>
+    <t>Order Status Report</t>
+  </si>
+  <si>
+    <t>Please find attached the order status report for your DC.</t>
+  </si>
+  <si>
+    <t>TMP002</t>
+  </si>
+  <si>
+    <t>Error Notification</t>
+  </si>
+  <si>
+    <t>An error occurred during order processing. Please review the details.</t>
+  </si>
+  <si>
+    <t>ProcessingRule</t>
+  </si>
+  <si>
+    <t>Ready for invoicing</t>
+  </si>
+  <si>
+    <t>Pending verification</t>
+  </si>
+  <si>
+    <t>ORD004</t>
+  </si>
+  <si>
+    <t>ORD005</t>
+  </si>
+  <si>
+    <t>DC04</t>
+  </si>
+  <si>
+    <t>ORD006</t>
+  </si>
+  <si>
+    <t>DC05</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="177" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,23 +216,83 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -137,6 +363,14 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,95 +658,128 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OrderID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>StatusCode</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DistributionCenter</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>OrderDate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ORD001</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
         <v>560</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DC01</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ORD002</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>575</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DC02</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2024-01-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ORD003</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
         <v>560</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DC03</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2024-01-12</t>
-        </is>
-      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="8">
+        <v>550</v>
+      </c>
+      <c r="D5" s="9">
+        <v>45304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1">
+      <c r="A6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="8">
+        <v>575</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="9">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="6">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" ht="15">
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="4:4" ht="15">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="4:4" ht="15">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="4:4" ht="15">
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="4:4" ht="15">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="4:4" ht="15">
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="4:4" ht="15">
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="4:4" ht="15">
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="4:4" ht="15">
+      <c r="D16" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -520,78 +787,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ErrorID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>OrderID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ErrorDescription</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ERR001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ORD002</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Failed to update status</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2024-01-11 10:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ERR002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ORD003</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Incomplete transaction</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2024-01-12 14:15</t>
-        </is>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -600,63 +839,41 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Username</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>AccessLevel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>user_dc01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>user_dc02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Operator</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Restricted</t>
-        </is>
+    <row r="1" spans="1:3" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -665,63 +882,41 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TemplateID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Body</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TMP001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Order Status Report</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Please find attached the order status report for your DC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TMP002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Error Notification</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>An error occurred during order processing. Please review the details.</t>
-        </is>
+    <row r="1" spans="1:3" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -730,44 +925,32 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>StatusCode</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ProcessingRule</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:2" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15">
+      <c r="A2">
         <v>560</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ready for invoicing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15">
+      <c r="A3">
         <v>575</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pending verification</t>
-        </is>
+      <c r="B3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Database/Automation_856_Workflow_Data.xlsx
+++ b/Database/Automation_856_Workflow_Data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>OrderID</t>
   </si>
@@ -163,6 +163,15 @@
   </si>
   <si>
     <t>DC05</t>
+  </si>
+  <si>
+    <t>ORD007</t>
+  </si>
+  <si>
+    <t>ORD008</t>
+  </si>
+  <si>
+    <t>ORD009</t>
   </si>
 </sst>
 </file>
@@ -173,7 +182,7 @@
     <numFmt numFmtId="177" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="178" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +199,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -251,7 +266,7 @@
       <alignment/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment/>
     </xf>
@@ -273,16 +288,20 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
       <protection/>
     </xf>
   </cellXfs>
@@ -659,8 +678,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="16.2857142857143" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15">
       <c r="A1" s="1" t="s">
@@ -754,17 +776,61 @@
         <v>45305</v>
       </c>
     </row>
-    <row r="8" spans="4:4" ht="15">
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="4:4" ht="15">
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="4:4" ht="15">
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="4:4" ht="15">
-      <c r="D11" s="6"/>
+    <row r="8" spans="1:4" ht="15" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8">
+        <v>560</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="9">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="8">
+        <v>560</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="9">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="8">
+        <v>560</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="9">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="8">
+        <v>560</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="9">
+        <v>45305</v>
+      </c>
     </row>
     <row r="12" spans="4:4" ht="15">
       <c r="D12" s="6"/>
@@ -885,6 +951,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15">
       <c r="A1" s="1" t="s">
@@ -928,6 +997,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="9.42428571428571" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="1" t="s">
